--- a/artfynd/A 4358-2025 artfynd.xlsx
+++ b/artfynd/A 4358-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,64 +680,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113936318</v>
+        <v>137510157</v>
       </c>
       <c r="B2" t="n">
-        <v>57144</v>
+        <v>107920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ljungögontröst</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Euphrasia micrantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långemysten, Vg</t>
+          <t>Långemysten, söder om i vägkant, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>369654</v>
+        <v>369492</v>
       </c>
       <c r="R2" t="n">
-        <v>6416221</v>
+        <v>6416117</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +757,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ca 10 plantor i norra vägkanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +776,271 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Nyberg</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Nyberg</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137510157</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137510233</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107920</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>626</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ljungögontröst</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Euphrasia micrantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>LÅngemysten, söder om, i vägkant, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>369518</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6416120</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett 30-tal blommande plantor i norra vägkanten.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137510233</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113936318</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långemysten, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>369654</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6416221</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-01-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-01-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Nyberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Nyberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113936318</t>
         </is>
@@ -809,6 +1049,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4358-2025 artfynd.xlsx
+++ b/artfynd/A 4358-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137510157</v>
       </c>
       <c r="B2" t="n">
-        <v>107920</v>
+        <v>107924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>137510233</v>
       </c>
       <c r="B3" t="n">
-        <v>107920</v>
+        <v>107924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
